--- a/Ver4.0/BOM/BOM.xlsx
+++ b/Ver4.0/BOM/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\stm32\STM-C4\Ver4.0\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Works\Projects\STM-C4\Ver4.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3DD5E3-B4AC-4C02-8968-7F317155D26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A872E824-CE1D-4050-B6AD-798F5A429ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1500" yWindow="1500" windowWidth="20556" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -411,10 +411,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KF2510连接线</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>电源线</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -502,6 +498,10 @@
   </si>
   <si>
     <t>或者 2-7V，或者包含5V的就行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KF2510连接线-2p</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2958,7 +2958,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>7</v>
@@ -2977,16 +2977,16 @@
     </row>
     <row r="3" spans="2:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -3036,7 +3036,7 @@
     </row>
     <row r="8" spans="2:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>60</v>
@@ -3045,7 +3045,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3093,14 +3093,14 @@
     </row>
     <row r="13" spans="2:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -3193,13 +3193,13 @@
         <v>240</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -3227,7 +3227,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -3488,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -3514,7 +3514,7 @@
     </row>
     <row r="47" spans="2:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -3556,7 +3556,7 @@
     </row>
     <row r="53" spans="2:6" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="2"/>
